--- a/Figure 6/Figure 6-A.xlsx
+++ b/Figure 6/Figure 6-A.xlsx
@@ -5,20 +5,29 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\图6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\iMetaOmics20260210\Figure 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4C53BCB-7D53-4FE9-8702-99CAA461870D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77E355F2-5251-4537-A0E2-414B421BBF86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24460" yWindow="830" windowWidth="19500" windowHeight="15580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28790" yWindow="4080" windowWidth="16730" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -50,10 +59,8 @@
         <vertAlign val="superscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>6</t>
     </r>
@@ -61,9 +68,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 1</t>
     </r>
@@ -78,10 +84,8 @@
         <vertAlign val="superscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>6</t>
     </r>
@@ -89,9 +93,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 2</t>
     </r>
@@ -106,10 +109,8 @@
         <vertAlign val="superscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>6</t>
     </r>
@@ -117,9 +118,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 3</t>
     </r>
@@ -134,10 +134,8 @@
         <vertAlign val="superscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>6</t>
     </r>
@@ -145,9 +143,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 4</t>
     </r>
@@ -162,10 +159,8 @@
         <vertAlign val="superscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>6</t>
     </r>
@@ -173,9 +168,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 5</t>
     </r>
@@ -190,10 +184,8 @@
         <vertAlign val="superscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>6</t>
     </r>
@@ -201,9 +193,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 6</t>
     </r>
@@ -218,10 +209,8 @@
         <vertAlign val="superscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>7</t>
     </r>
@@ -229,9 +218,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 1</t>
     </r>
@@ -246,10 +234,8 @@
         <vertAlign val="superscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>7</t>
     </r>
@@ -257,9 +243,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 2</t>
     </r>
@@ -274,10 +259,8 @@
         <vertAlign val="superscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>7</t>
     </r>
@@ -285,9 +268,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 3</t>
     </r>
@@ -302,10 +284,8 @@
         <vertAlign val="superscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>7</t>
     </r>
@@ -313,9 +293,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 4</t>
     </r>
@@ -330,10 +309,8 @@
         <vertAlign val="superscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>7</t>
     </r>
@@ -341,9 +318,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 5</t>
     </r>
@@ -358,10 +334,8 @@
         <vertAlign val="superscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>7</t>
     </r>
@@ -369,9 +343,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 6</t>
     </r>
@@ -386,10 +359,8 @@
         <vertAlign val="superscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>8</t>
     </r>
@@ -397,9 +368,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 1</t>
     </r>
@@ -414,10 +384,8 @@
         <vertAlign val="superscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>8</t>
     </r>
@@ -425,9 +393,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 2</t>
     </r>
@@ -442,10 +409,8 @@
         <vertAlign val="superscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>8</t>
     </r>
@@ -453,9 +418,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 3</t>
     </r>
@@ -470,10 +434,8 @@
         <vertAlign val="superscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>8</t>
     </r>
@@ -481,9 +443,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 4</t>
     </r>
@@ -498,10 +459,8 @@
         <vertAlign val="superscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>8</t>
     </r>
@@ -509,9 +468,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 5</t>
     </r>
@@ -526,10 +484,8 @@
         <vertAlign val="superscript"/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>8</t>
     </r>
@@ -537,9 +493,8 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="等线"/>
-        <family val="2"/>
-        <scheme val="minor"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> 6</t>
     </r>
@@ -553,7 +508,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -569,13 +524,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <vertAlign val="superscript"/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -600,8 +559,8 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -885,225 +844,225 @@
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="2"/>
     <col min="2" max="2" width="12.25" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B1" t="s">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="2">
         <v>0.83388594164456253</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="2">
         <v>0.47609868928296067</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="2">
         <v>0.70258620689655171</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="2">
         <v>0.61719352351580581</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="2">
         <v>1.187997347480106</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="2">
         <v>0.64263685427910544</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="2">
         <v>1.1064323607427056</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="2">
         <v>0.66345412490362332</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="2">
         <v>1.1462201591511936</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="2">
         <v>0.6773323053199688</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="2">
         <v>1.0925066312997349</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="2">
         <v>0.67501927525057781</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="2">
         <v>0.97513262599469508</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="2">
         <v>0.47378565921356935</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="2">
         <v>1.1641246684350133</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="2">
         <v>0.56630686198920543</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="2">
         <v>1.1004641909814323</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="2">
         <v>0.68195836545875055</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="2">
         <v>1.0726127320954908</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="2">
         <v>0.65882806476484157</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="2">
         <v>1.124336870026525</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="2">
         <v>0.52004626060138737</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="2">
         <v>1.0586870026525199</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="2">
         <v>0.52004626060138737</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="2">
         <v>0.82990716180371382</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="2">
         <v>0.6773323053199688</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="2">
         <v>0.88163129973474808</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="2">
         <v>0.33269082498072422</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="2">
         <v>0.90152519893899208</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="2">
         <v>0.30262143407864245</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="2">
         <v>0.825928381962865</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="2">
         <v>0.36044718581341512</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="2">
         <v>1.9181034482758617</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" s="2">
         <v>0.15227447956823373</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="2">
         <v>0.69064986737400558</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="2">
         <v>0.32575173477255154</v>
       </c>
     </row>
